--- a/rtos-api-analysis/results/memory/ThreadX_memory_and_coverage_analysis.xlsx
+++ b/rtos-api-analysis/results/memory/ThreadX_memory_and_coverage_analysis.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
         <v>1076</v>
       </c>
       <c r="C2" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="D2" t="n">
         <v>0.04</v>
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>342007</v>
+        <v>7328</v>
       </c>
       <c r="C3" t="n">
-        <v>10.33</v>
+        <v>3.04</v>
       </c>
       <c r="D3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="4">
@@ -493,7 +493,7 @@
         <v>13584</v>
       </c>
       <c r="C4" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="D4" t="n">
         <v>0.96</v>
@@ -502,913 +502,1489 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>semaphore_put</t>
+          <t>module_object_allocate</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41930</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>2.94</v>
+        <v>1.44</v>
       </c>
       <c r="D5" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>semaphore_create</t>
+          <t>block_pool_performance_info_get</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4100</v>
+        <v>2296</v>
       </c>
       <c r="C6" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>queue_send_notify</t>
+          <t>semaphore_put</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1933</v>
+        <v>41738</v>
       </c>
       <c r="C7" t="n">
-        <v>2.79</v>
+        <v>3.12</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>thread_terminate</t>
+          <t>txm_module_application_request</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>950</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
-        <v>2.14</v>
+        <v>1.45</v>
       </c>
       <c r="D8" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>byte_release</t>
+          <t>semaphore_create</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94164</v>
+        <v>4100</v>
       </c>
       <c r="C9" t="n">
-        <v>3.88</v>
+        <v>1.92</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>byte_pool_create</t>
+          <t>module_object_pointer_get</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5163</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mutex_info_get</t>
+          <t>queue_send_notify</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24716</v>
+        <v>1933</v>
       </c>
       <c r="C11" t="n">
-        <v>1.97</v>
+        <v>2.79</v>
       </c>
       <c r="D11" t="n">
-        <v>0.96</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>thread_relinquish</t>
+          <t>thread_terminate</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="C12" t="n">
-        <v>1.55</v>
+        <v>2.13</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>semaphore_prioritize</t>
+          <t>trace_isr_enter_insert</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3792</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="D13" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>thread_delete</t>
+          <t>byte_release</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>638</v>
+        <v>104466</v>
       </c>
       <c r="C14" t="n">
-        <v>3.76</v>
+        <v>4.26</v>
       </c>
       <c r="D14" t="n">
-        <v>0.04</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>thread_reset</t>
+          <t>byte_pool_create</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4928</v>
+        <v>5163</v>
       </c>
       <c r="C15" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>block_allocate</t>
+          <t>semaphore_performance_info_get</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3420</v>
+        <v>2296</v>
       </c>
       <c r="C16" t="n">
-        <v>2.53</v>
+        <v>1.7</v>
       </c>
       <c r="D16" t="n">
-        <v>0.21</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>queue_send</t>
+          <t>thread_stack_error_notify</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>338062</v>
+        <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>10.16</v>
+        <v>1.45</v>
       </c>
       <c r="D17" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>timer_create</t>
+          <t>mutex_info_get</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25391</v>
+        <v>24716</v>
       </c>
       <c r="C18" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="D18" t="n">
-        <v>0.28</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>thread_create</t>
+          <t>thread_relinquish</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>42891</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>20.12</v>
+        <v>1.55</v>
       </c>
       <c r="D19" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>timer_change</t>
+          <t>semaphore_prioritize</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1278</v>
+        <v>3792</v>
       </c>
       <c r="C20" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="D20" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mutex_put</t>
+          <t>time_get</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14057627</v>
+        <v>11</v>
       </c>
       <c r="C21" t="n">
-        <v>207.04</v>
+        <v>1.48</v>
       </c>
       <c r="D21" t="n">
-        <v>0.72</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>semaphore_get</t>
+          <t>semaphore_performance_system_info_get</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2320</v>
+        <v>235</v>
       </c>
       <c r="C22" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="D22" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>thread_time_slice_change</t>
+          <t>thread_delete</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1482</v>
+        <v>638</v>
       </c>
       <c r="C23" t="n">
-        <v>1.73</v>
+        <v>3.77</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>thread_wait_abort</t>
+          <t>thread_reset</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>50666</v>
+        <v>4928</v>
       </c>
       <c r="C24" t="n">
-        <v>2.84</v>
+        <v>1.86</v>
       </c>
       <c r="D24" t="n">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>thread_entry_exit_notify</t>
+          <t>block_allocate</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2055</v>
+        <v>3420</v>
       </c>
       <c r="C25" t="n">
-        <v>2.82</v>
+        <v>2.54</v>
       </c>
       <c r="D25" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>queue_prioritize</t>
+          <t>trace_enable</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3792</v>
+        <v>42</v>
       </c>
       <c r="C26" t="n">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
       <c r="D26" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>queue_delete</t>
+          <t>mutex_performance_info_get</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1166</v>
+        <v>3218</v>
       </c>
       <c r="C27" t="n">
-        <v>3.86</v>
+        <v>1.75</v>
       </c>
       <c r="D27" t="n">
-        <v>0.04</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>byte_allocate</t>
+          <t>queue_send</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6058</v>
+        <v>1768</v>
       </c>
       <c r="C28" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="D28" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mutex_delete</t>
+          <t>timer_create</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1076</v>
+        <v>25233</v>
       </c>
       <c r="C29" t="n">
-        <v>3.86</v>
+        <v>3.69</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mutex_prioritize</t>
+          <t>thread_create</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3792</v>
+        <v>42891</v>
       </c>
       <c r="C30" t="n">
-        <v>1.95</v>
+        <v>20.14</v>
       </c>
       <c r="D30" t="n">
-        <v>0.79</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>block_pool_prioritize</t>
+          <t>byte_pool_performance_system_info_get</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3792</v>
+        <v>403</v>
       </c>
       <c r="C31" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="D31" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>block_pool_delete</t>
+          <t>event_flags_performance_info_get</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1076</v>
+        <v>2296</v>
       </c>
       <c r="C32" t="n">
-        <v>3.86</v>
+        <v>1.7</v>
       </c>
       <c r="D32" t="n">
-        <v>0.04</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>event_flags_create</t>
+          <t>timer_change</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3764</v>
+        <v>1278</v>
       </c>
       <c r="C33" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="D33" t="n">
-        <v>0.87</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>queue_receive</t>
+          <t>module_callback_request_thread_entry</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>166798</v>
+        <v>17</v>
       </c>
       <c r="C34" t="n">
-        <v>5.39</v>
+        <v>1.46</v>
       </c>
       <c r="D34" t="n">
-        <v>0.49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>semaphore_ceiling_put</t>
+          <t>mutex_put</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>42742</v>
+        <v>11587055</v>
       </c>
       <c r="C35" t="n">
-        <v>2.97</v>
+        <v>206.48</v>
       </c>
       <c r="D35" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>byte_pool_delete</t>
+          <t>module_thread_system_suspend</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1076</v>
+        <v>17</v>
       </c>
       <c r="C36" t="n">
-        <v>3.86</v>
+        <v>1.43</v>
       </c>
       <c r="D36" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>byte_pool_info_get</t>
+          <t>semaphore_get</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>24740</v>
+        <v>2320</v>
       </c>
       <c r="C37" t="n">
-        <v>1.97</v>
+        <v>2.44</v>
       </c>
       <c r="D37" t="n">
-        <v>0.96</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>thread_resume</t>
+          <t>thread_time_slice_change</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18170</v>
+        <v>1482</v>
       </c>
       <c r="C38" t="n">
-        <v>2.33</v>
+        <v>1.71</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mutex_create</t>
+          <t>thread_wait_abort</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6358</v>
+        <v>34610</v>
       </c>
       <c r="C39" t="n">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="D39" t="n">
-        <v>0.17</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>byte_pool_prioritize</t>
+          <t>time_set</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3792</v>
+        <v>51</v>
       </c>
       <c r="C40" t="n">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
       <c r="D40" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>semaphore_info_get</t>
+          <t>trace_event_unfilter</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>13464</v>
+        <v>52</v>
       </c>
       <c r="C41" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="D41" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>semaphore_put_notify</t>
+          <t>thread_entry_exit_notify</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1933</v>
+        <v>2055</v>
       </c>
       <c r="C42" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>timer_info_get</t>
+          <t>queue_performance_info_get</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>69470</v>
+        <v>3218</v>
       </c>
       <c r="C43" t="n">
-        <v>2.29</v>
+        <v>1.75</v>
       </c>
       <c r="D43" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>block_pool_info_get</t>
+          <t>trace_event_filter</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24764</v>
+        <v>52</v>
       </c>
       <c r="C44" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="D44" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>thread_suspend</t>
+          <t>queue_prioritize</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5438</v>
+        <v>3792</v>
       </c>
       <c r="C45" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="D45" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>queue_info_get</t>
+          <t>queue_delete</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24764</v>
+        <v>1166</v>
       </c>
       <c r="C46" t="n">
-        <v>1.96</v>
+        <v>3.84</v>
       </c>
       <c r="D46" t="n">
-        <v>0.96</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>event_flags_set_notify</t>
+          <t>thread_sleep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1933</v>
+        <v>82</v>
       </c>
       <c r="C47" t="n">
-        <v>2.79</v>
+        <v>1.85</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>thread_preemption_change</t>
+          <t>timer_performance_info_get</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1494</v>
+        <v>2754</v>
       </c>
       <c r="C48" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="D48" t="n">
-        <v>0.46</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>block_release</t>
+          <t>byte_allocate</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>6628</v>
       </c>
       <c r="C49" t="n">
-        <v>1.8</v>
+        <v>2.83</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>thread_priority_change</t>
+          <t>mutex_delete</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1722</v>
+        <v>1076</v>
       </c>
       <c r="C50" t="n">
-        <v>2.37</v>
+        <v>3.85</v>
       </c>
       <c r="D50" t="n">
-        <v>0.14</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>timer_activate</t>
+          <t>mutex_prioritize</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5431</v>
+        <v>3792</v>
       </c>
       <c r="C51" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="D51" t="n">
-        <v>0.95</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>timer_deactivate</t>
+          <t>block_pool_prioritize</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10470</v>
+        <v>3792</v>
       </c>
       <c r="C52" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>thread_info_get</t>
+          <t>block_pool_delete</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>89772</v>
+        <v>1076</v>
       </c>
       <c r="C53" t="n">
-        <v>2.3</v>
+        <v>3.84</v>
       </c>
       <c r="D53" t="n">
-        <v>0.97</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>mutex_get</t>
+          <t>event_flags_create</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>5494</v>
+        <v>3764</v>
       </c>
       <c r="C54" t="n">
-        <v>2.78</v>
+        <v>1.91</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>block_pool_create</t>
+          <t>block_pool_performance_system_info_get</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6629</v>
+        <v>235</v>
       </c>
       <c r="C55" t="n">
-        <v>2.14</v>
+        <v>1.56</v>
       </c>
       <c r="D55" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>queue_flush</t>
+          <t>module_object_deallocate</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25273</v>
+        <v>17</v>
       </c>
       <c r="C56" t="n">
-        <v>2.67</v>
+        <v>1.44</v>
       </c>
       <c r="D56" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>event_flags_set</t>
+          <t>queue_performance_system_info_get</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>200748</v>
+        <v>346</v>
       </c>
       <c r="C57" t="n">
-        <v>6.23</v>
+        <v>1.6</v>
       </c>
       <c r="D57" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>event_flags_get</t>
+          <t>queue_receive</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>12975</v>
+        <v>166798</v>
       </c>
       <c r="C58" t="n">
-        <v>2.67</v>
+        <v>5.79</v>
       </c>
       <c r="D58" t="n">
-        <v>0.26</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>queue_create</t>
+          <t>semaphore_ceiling_put</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>6523</v>
+        <v>42502</v>
       </c>
       <c r="C59" t="n">
-        <v>2.01</v>
+        <v>3.15</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>semaphore_delete</t>
+          <t>timer_performance_system_info_get</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1166</v>
+        <v>290</v>
       </c>
       <c r="C60" t="n">
-        <v>3.86</v>
+        <v>1.58</v>
       </c>
       <c r="D60" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>timer_delete</t>
+          <t>byte_pool_delete</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1076</v>
       </c>
       <c r="C61" t="n">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="D61" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>byte_pool_info_get</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>24740</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>thread_resume</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>18170</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>mutex_create</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>6338</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>byte_pool_prioritize</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3792</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>semaphore_info_get</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>13464</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>byte_pool_performance_info_get</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3688</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>semaphore_put_notify</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1933</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>timer_info_get</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>68537</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>block_pool_info_get</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>24764</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>thread_suspend</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>5438</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>queue_info_get</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>24764</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>event_flags_set_notify</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1933</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>trace_disable</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>11</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>thread_preemption_change</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1494</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>block_release</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>166</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>trace_interrupt_control</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>26</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>thread_priority_change</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1722</v>
+      </c>
+      <c r="C78" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>timer_activate</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>5312</v>
+      </c>
+      <c r="C79" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>trace_buffer_full_notify</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>53</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>module_object_pointer_get_extended</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>41</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>timer_deactivate</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>11083</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>thread_performance_system_info_get</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>641</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>thread_info_get</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>89772</v>
+      </c>
+      <c r="C84" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>mutex_get</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>5494</v>
+      </c>
+      <c r="C85" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>block_pool_create</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>6629</v>
+      </c>
+      <c r="C86" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>thread_performance_info_get</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>5134</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>queue_flush</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>25273</v>
+      </c>
+      <c r="C88" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>trace_user_event_insert</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>171</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>event_flags_set</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>198336</v>
+      </c>
+      <c r="C90" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>event_flags_get</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>12975</v>
+      </c>
+      <c r="C91" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>queue_create</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>6523</v>
+      </c>
+      <c r="C92" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>event_flags_performance_system_info_get</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>235</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>semaphore_delete</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1166</v>
+      </c>
+      <c r="C94" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>timer_delete</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1076</v>
+      </c>
+      <c r="C95" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>thread_interrupt_control</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>26</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>mutex_performance_system_info_get</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>346</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1479,34 +2055,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>395.96</v>
+        <v>439.72</v>
       </c>
       <c r="B2" t="n">
-        <v>6.5993</v>
+        <v>4.5804</v>
       </c>
       <c r="C2" t="n">
-        <v>207.04</v>
+        <v>206.48</v>
       </c>
       <c r="D2" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="E2" t="n">
-        <v>26.4605</v>
+        <v>20.9247</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5315</v>
+        <v>0.68</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.2604</v>
       </c>
       <c r="H2" t="n">
-        <v>0.15</v>
+        <v>0.0833</v>
       </c>
       <c r="I2" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>

--- a/rtos-api-analysis/results/memory/ThreadX_memory_and_coverage_analysis.xlsx
+++ b/rtos-api-analysis/results/memory/ThreadX_memory_and_coverage_analysis.xlsx
@@ -461,7 +461,7 @@
         <v>1076</v>
       </c>
       <c r="C2" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="D2" t="n">
         <v>0.04</v>
@@ -474,10 +474,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7328</v>
+        <v>6547</v>
       </c>
       <c r="C3" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="D3" t="n">
         <v>0.44</v>
@@ -493,7 +493,7 @@
         <v>13584</v>
       </c>
       <c r="C4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="D4" t="n">
         <v>0.96</v>
@@ -525,7 +525,7 @@
         <v>2296</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="D6" t="n">
         <v>0.9399999999999999</v>
@@ -541,7 +541,7 @@
         <v>41738</v>
       </c>
       <c r="C7" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="D7" t="n">
         <v>0.8100000000000001</v>
@@ -573,7 +573,7 @@
         <v>4100</v>
       </c>
       <c r="C9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="D9" t="n">
         <v>0.88</v>
@@ -621,7 +621,7 @@
         <v>950</v>
       </c>
       <c r="C12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="D12" t="n">
         <v>0.15</v>
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104466</v>
+        <v>94164</v>
       </c>
       <c r="C14" t="n">
-        <v>4.26</v>
+        <v>3.88</v>
       </c>
       <c r="D14" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -685,7 +685,7 @@
         <v>2296</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="D16" t="n">
         <v>0.9399999999999999</v>
@@ -717,7 +717,7 @@
         <v>24716</v>
       </c>
       <c r="C18" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="D18" t="n">
         <v>0.96</v>
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3792</v>
+        <v>4012</v>
       </c>
       <c r="C20" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="D20" t="n">
         <v>0.79</v>
@@ -765,7 +765,7 @@
         <v>11</v>
       </c>
       <c r="C21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="D21" t="n">
         <v>0.2</v>
@@ -781,7 +781,7 @@
         <v>235</v>
       </c>
       <c r="C22" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -797,7 +797,7 @@
         <v>638</v>
       </c>
       <c r="C23" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="D23" t="n">
         <v>0.04</v>
@@ -813,7 +813,7 @@
         <v>4928</v>
       </c>
       <c r="C24" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="D24" t="n">
         <v>0.9399999999999999</v>
@@ -829,7 +829,7 @@
         <v>3420</v>
       </c>
       <c r="C25" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="D25" t="n">
         <v>0.21</v>
@@ -845,7 +845,7 @@
         <v>42</v>
       </c>
       <c r="C26" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -861,7 +861,7 @@
         <v>3218</v>
       </c>
       <c r="C27" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="D27" t="n">
         <v>0.95</v>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1768</v>
+        <v>12025</v>
       </c>
       <c r="C28" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="D28" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="29">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25233</v>
+        <v>25403</v>
       </c>
       <c r="C29" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="D29" t="n">
         <v>0.28</v>
@@ -909,7 +909,7 @@
         <v>42891</v>
       </c>
       <c r="C30" t="n">
-        <v>20.14</v>
+        <v>20.12</v>
       </c>
       <c r="D30" t="n">
         <v>0.05</v>
@@ -925,7 +925,7 @@
         <v>403</v>
       </c>
       <c r="C31" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -941,7 +941,7 @@
         <v>2296</v>
       </c>
       <c r="C32" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="D32" t="n">
         <v>0.9399999999999999</v>
@@ -957,7 +957,7 @@
         <v>1278</v>
       </c>
       <c r="C33" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="D33" t="n">
         <v>0.71</v>
@@ -973,7 +973,7 @@
         <v>17</v>
       </c>
       <c r="C34" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11587055</v>
+        <v>18660651</v>
       </c>
       <c r="C35" t="n">
-        <v>206.48</v>
+        <v>273.79</v>
       </c>
       <c r="D35" t="n">
         <v>0.72</v>
@@ -1037,7 +1037,7 @@
         <v>1482</v>
       </c>
       <c r="C38" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="D38" t="n">
         <v>0.7</v>
@@ -1053,7 +1053,7 @@
         <v>34610</v>
       </c>
       <c r="C39" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="D39" t="n">
         <v>0.83</v>
@@ -1117,7 +1117,7 @@
         <v>3218</v>
       </c>
       <c r="C43" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="D43" t="n">
         <v>0.95</v>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3792</v>
+        <v>4012</v>
       </c>
       <c r="C45" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="D45" t="n">
         <v>0.79</v>
@@ -1165,7 +1165,7 @@
         <v>1166</v>
       </c>
       <c r="C46" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="D46" t="n">
         <v>0.04</v>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6628</v>
+        <v>6058</v>
       </c>
       <c r="C49" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="D49" t="n">
         <v>0.28</v>
@@ -1229,7 +1229,7 @@
         <v>1076</v>
       </c>
       <c r="C50" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="D50" t="n">
         <v>0.04</v>
@@ -1242,10 +1242,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3792</v>
+        <v>4012</v>
       </c>
       <c r="C51" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="D51" t="n">
         <v>0.79</v>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3792</v>
+        <v>4012</v>
       </c>
       <c r="C52" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="D52" t="n">
         <v>0.79</v>
@@ -1277,7 +1277,7 @@
         <v>1076</v>
       </c>
       <c r="C53" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="D53" t="n">
         <v>0.04</v>
@@ -1293,7 +1293,7 @@
         <v>3764</v>
       </c>
       <c r="C54" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="D54" t="n">
         <v>0.87</v>
@@ -1309,7 +1309,7 @@
         <v>235</v>
       </c>
       <c r="C55" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -1325,7 +1325,7 @@
         <v>17</v>
       </c>
       <c r="C56" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>166798</v>
       </c>
       <c r="C58" t="n">
-        <v>5.79</v>
+        <v>5.39</v>
       </c>
       <c r="D58" t="n">
         <v>0.49</v>
@@ -1373,7 +1373,7 @@
         <v>42502</v>
       </c>
       <c r="C59" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="D59" t="n">
         <v>0.83</v>
@@ -1389,7 +1389,7 @@
         <v>290</v>
       </c>
       <c r="C60" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
@@ -1405,7 +1405,7 @@
         <v>1076</v>
       </c>
       <c r="C61" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="D61" t="n">
         <v>0.04</v>
@@ -1421,7 +1421,7 @@
         <v>24740</v>
       </c>
       <c r="C62" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="D62" t="n">
         <v>0.96</v>
@@ -1437,7 +1437,7 @@
         <v>18170</v>
       </c>
       <c r="C63" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="D63" t="n">
         <v>0.8</v>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6338</v>
+        <v>6358</v>
       </c>
       <c r="C64" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="D64" t="n">
         <v>0.17</v>
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3792</v>
+        <v>4012</v>
       </c>
       <c r="C65" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="D65" t="n">
         <v>0.79</v>
@@ -1485,7 +1485,7 @@
         <v>13464</v>
       </c>
       <c r="C66" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="D66" t="n">
         <v>0.96</v>
@@ -1501,7 +1501,7 @@
         <v>3688</v>
       </c>
       <c r="C67" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="D67" t="n">
         <v>0.96</v>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>68537</v>
+        <v>68530</v>
       </c>
       <c r="C69" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="D69" t="n">
         <v>0.96</v>
@@ -1549,7 +1549,7 @@
         <v>24764</v>
       </c>
       <c r="C70" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="D70" t="n">
         <v>0.96</v>
@@ -1565,7 +1565,7 @@
         <v>5438</v>
       </c>
       <c r="C71" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="D71" t="n">
         <v>0.55</v>
@@ -1581,7 +1581,7 @@
         <v>24764</v>
       </c>
       <c r="C72" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="D72" t="n">
         <v>0.96</v>
@@ -1613,7 +1613,7 @@
         <v>11</v>
       </c>
       <c r="C74" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="D74" t="n">
         <v>0.41</v>
@@ -1629,7 +1629,7 @@
         <v>1494</v>
       </c>
       <c r="C75" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="D75" t="n">
         <v>0.46</v>
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="D76" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -1661,7 +1661,7 @@
         <v>26</v>
       </c>
       <c r="C77" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
@@ -1677,7 +1677,7 @@
         <v>1722</v>
       </c>
       <c r="C78" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="D78" t="n">
         <v>0.14</v>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>5312</v>
+        <v>5383</v>
       </c>
       <c r="C79" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="D79" t="n">
         <v>0.95</v>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>11083</v>
+        <v>12064</v>
       </c>
       <c r="C82" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
         <v>0.9399999999999999</v>
@@ -1773,7 +1773,7 @@
         <v>89772</v>
       </c>
       <c r="C84" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="D84" t="n">
         <v>0.97</v>
@@ -1789,7 +1789,7 @@
         <v>5494</v>
       </c>
       <c r="C85" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D85" t="n">
         <v>0.2</v>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6629</v>
+        <v>6953</v>
       </c>
       <c r="C86" t="n">
         <v>2.14</v>
@@ -1821,7 +1821,7 @@
         <v>5134</v>
       </c>
       <c r="C87" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="D87" t="n">
         <v>0.97</v>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>25273</v>
+        <v>41559</v>
       </c>
       <c r="C88" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="D88" t="n">
         <v>0.84</v>
@@ -1866,13 +1866,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>198336</v>
+        <v>222510</v>
       </c>
       <c r="C90" t="n">
-        <v>6.89</v>
+        <v>6.41</v>
       </c>
       <c r="D90" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="91">
@@ -1917,7 +1917,7 @@
         <v>235</v>
       </c>
       <c r="C93" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
@@ -1933,7 +1933,7 @@
         <v>1166</v>
       </c>
       <c r="C94" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="D94" t="n">
         <v>0.04</v>
@@ -1949,7 +1949,7 @@
         <v>1076</v>
       </c>
       <c r="C95" t="n">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="D95" t="n">
         <v>0.04</v>
@@ -1965,7 +1965,7 @@
         <v>26</v>
       </c>
       <c r="C96" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
@@ -2055,34 +2055,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>439.72</v>
+        <v>504.64</v>
       </c>
       <c r="B2" t="n">
-        <v>4.5804</v>
+        <v>5.2567</v>
       </c>
       <c r="C2" t="n">
-        <v>206.48</v>
+        <v>273.79</v>
       </c>
       <c r="D2" t="n">
         <v>1.43</v>
       </c>
       <c r="E2" t="n">
-        <v>20.9247</v>
+        <v>27.7705</v>
       </c>
       <c r="F2" t="n">
-        <v>0.68</v>
+        <v>0.6792</v>
       </c>
       <c r="G2" t="n">
         <v>0.2604</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0833</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
